--- a/business_forms/048_storage_facility_incident_form--business_forms.xlsx
+++ b/business_forms/048_storage_facility_incident_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,8 +911,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -940,12 +940,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fire'}</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fire'}</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'theft'}</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Theft'}</t>
+          <t>Theft</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'environmental'}</t>
+          <t>environmental</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Environmental'}</t>
+          <t>Environmental</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_manager'}</t>
+          <t>facility_manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility Manager'}</t>
+          <t>Facility Manager</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'no_action_needed'}</t>
+          <t>no_action_needed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'No Action Needed'}</t>
+          <t>No Action Needed</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'review_and_investigate'}</t>
+          <t>review_and_investigate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Review and Investigate'}</t>
+          <t>Review and Investigate</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'escalate'}</t>
+          <t>escalate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Escalate'}</t>
+          <t>Escalate</t>
         </is>
       </c>
     </row>
